--- a/htr-strucGenerale-CDA/ig/StructureDefinition-Responsable.xlsx
+++ b/htr-strucGenerale-CDA/ig/StructureDefinition-Responsable.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-18T10:35:11+00:00</t>
+    <t>2025-04-18T14:53:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -239,10 +239,7 @@
     <t/>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>*</t>
+    <t>1</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -252,10 +249,13 @@
     <t>Base</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
     <t>Responsable.dateHeureAttestationValidite</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t xml:space="preserve">dateTime
@@ -740,19 +740,19 @@
         <v>73</v>
       </c>
       <c r="G2" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H2" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I2" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J2" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K2" t="s" s="2">
         <v>74</v>
-      </c>
-      <c r="H2" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I2" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J2" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K2" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="L2" t="s" s="2">
         <v>9</v>
@@ -809,13 +809,13 @@
         <v>72</v>
       </c>
       <c r="AF2" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG2" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="AG2" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="AH2" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>72</v>
@@ -826,10 +826,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -837,10 +837,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>72</v>
@@ -909,13 +909,13 @@
         <v>72</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>72</v>
@@ -937,10 +937,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>72</v>
@@ -1012,10 +1012,10 @@
         <v>81</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>72</v>

--- a/htr-strucGenerale-CDA/ig/StructureDefinition-Responsable.xlsx
+++ b/htr-strucGenerale-CDA/ig/StructureDefinition-Responsable.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-18T14:53:38+00:00</t>
+    <t>2025-04-22T14:34:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
